--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -107,49 +107,352 @@
     <t xml:space="preserve">level</t>
   </si>
   <si>
+    <t xml:space="preserve">2024M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-10-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal government jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-federal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial bankruptcy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">business-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administrative Office of the United States Courts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 12-month total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-12-sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USASpending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$123k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resident-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataFy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident spending, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resident-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpi-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research-hd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding obligated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States Patent and Trademark Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patent applications filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents-filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crunchbase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital volume ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor Market &amp; Workforce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">labor-market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct_diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, white workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-white</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024M4</t>
   </si>
   <si>
     <t xml:space="preserve">2026M4</t>
   </si>
   <si>
-    <t xml:space="preserve">DMV-2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal government jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-federal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial bankruptcy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">business-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administrative Office of the United States Courts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 12-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-12-sum</t>
+    <t xml:space="preserve">Unemployment rate, black workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, workers of color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-poc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, men</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-fte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internship postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-internships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mass layoff notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warn-notices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WarnTracker.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate &amp; Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real-estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial occupancy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoStar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied office space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]%</t>
   </si>
   <si>
     <t xml:space="preserve">2024Q1</t>
@@ -158,297 +461,6 @@
     <t xml:space="preserve">2026Q1</t>
   </si>
   <si>
-    <t xml:space="preserve">Federal obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USASpending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-04-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataFy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpi-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">research-hd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding obligated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States Patent and Trademark Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patent applications filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents-filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crunchbase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital volume ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor Market &amp; Workforce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labor-market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct_diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, white workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-white</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, black workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, workers of color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-poc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-fte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internship postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-internships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mass layoff notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warn-notices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WarnTracker.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate &amp; Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real-estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial occupancy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoStar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied office space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]%</t>
-  </si>
-  <si>
     <t xml:space="preserve">Occupied retail space (% SF)</t>
   </si>
   <si>
@@ -503,6 +515,18 @@
     <t xml:space="preserve">destination-travel</t>
   </si>
   <si>
+    <t xml:space="preserve">Hotel revenue per available room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotel-revpar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0.[00]</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total air passengers served</t>
   </si>
   <si>
@@ -518,6 +542,12 @@
     <t xml:space="preserve">air-passengers</t>
   </si>
   <si>
+    <t xml:space="preserve">2024M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M6</t>
+  </si>
+  <si>
     <t xml:space="preserve">Visitor spending</t>
   </si>
   <si>
@@ -539,18 +569,6 @@
     <t xml:space="preserve">overnight-visitors</t>
   </si>
   <si>
-    <t xml:space="preserve">Hotel revenue per available room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotel-revpar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.[00]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Municipal Services</t>
   </si>
   <si>
@@ -599,10 +617,10 @@
     <t xml:space="preserve">crime-rate-total</t>
   </si>
   <si>
-    <t xml:space="preserve">2024M5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M5</t>
+    <t xml:space="preserve">2024M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M9</t>
   </si>
   <si>
     <t xml:space="preserve">Violent crimes</t>
@@ -641,15 +659,6 @@
     <t xml:space="preserve">credit-constrained-nearprime</t>
   </si>
   <si>
-    <t xml:space="preserve">2024Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-05-01</t>
-  </si>
-  <si>
     <t xml:space="preserve">Severely credit-constrained consumers</t>
   </si>
   <si>
@@ -701,6 +710,72 @@
     <t xml:space="preserve">about</t>
   </si>
   <si>
+    <t xml:space="preserve">Educational attainment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eduatt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educational attaintment for population aged 25 and older</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Census Bureau and Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less than high school</t>
+  </si>
+  <si>
+    <t xml:space="preserve">less-than-hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">null</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2025-12-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High school or equivalent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">high-school</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some college or associate's degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">some-college-aa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor's degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bachelors-degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graduate or professional degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">graduate-degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High school degree or higher, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hs-plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor's degree or higher, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ba-plus</t>
+  </si>
+  <si>
     <t xml:space="preserve">Population</t>
   </si>
   <si>
@@ -710,76 +785,10 @@
     <t xml:space="preserve">Total population</t>
   </si>
   <si>
-    <t xml:space="preserve">U.S. Census Bureau and Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2025-12-11</t>
-  </si>
-  <si>
     <t xml:space="preserve">Share of foreign-born population (%)</t>
   </si>
   <si>
     <t xml:space="preserve">foreign-born</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educational attainment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eduatt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educational attaintment for population aged 25 and older</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Less than high school</t>
-  </si>
-  <si>
-    <t xml:space="preserve">less-than-hs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High school or equivalent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">high-school</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Some college or associate's degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">some-college-aa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bachelor's degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bachelors-degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graduate or professional degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">graduate-degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High school degree or higher, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hs-plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bachelor's degree or higher, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ba-plus</t>
   </si>
 </sst>
 </file>
@@ -1821,10 +1830,10 @@
         <v>45</v>
       </c>
       <c r="N13" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="O13" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1877,10 +1886,10 @@
         <v>45</v>
       </c>
       <c r="N14" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="O14" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1989,10 +1998,10 @@
         <v>69</v>
       </c>
       <c r="N16" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="O16" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
@@ -2024,10 +2033,10 @@
         <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I17" t="s">
         <v>26</v>
@@ -2045,10 +2054,10 @@
         <v>69</v>
       </c>
       <c r="N17" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="O17" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -2080,10 +2089,10 @@
         <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H18" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I18" t="s">
         <v>26</v>
@@ -2101,10 +2110,10 @@
         <v>69</v>
       </c>
       <c r="N18" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="O18" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -2136,10 +2145,10 @@
         <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I19" t="s">
         <v>26</v>
@@ -2157,10 +2166,10 @@
         <v>69</v>
       </c>
       <c r="N19" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="O19" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -2192,10 +2201,10 @@
         <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I20" t="s">
         <v>26</v>
@@ -2213,10 +2222,10 @@
         <v>69</v>
       </c>
       <c r="N20" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="O20" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -2236,22 +2245,22 @@
         <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G21" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H21" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I21" t="s">
         <v>26</v>
@@ -2292,22 +2301,22 @@
         <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I22" t="s">
         <v>26</v>
@@ -2348,22 +2357,22 @@
         <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G23" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H23" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I23" t="s">
         <v>26</v>
@@ -2404,22 +2413,22 @@
         <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G24" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I24" t="s">
         <v>26</v>
@@ -2460,22 +2469,22 @@
         <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G25" t="s">
         <v>134</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" t="s">
         <v>135</v>
-      </c>
-      <c r="G25" t="s">
-        <v>132</v>
-      </c>
-      <c r="H25" t="s">
-        <v>133</v>
       </c>
       <c r="I25" t="s">
         <v>26</v>
@@ -2510,34 +2519,34 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E26" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F26" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G26" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H26" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I26" t="s">
         <v>42</v>
       </c>
       <c r="J26" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K26" t="s">
         <v>109</v>
@@ -2549,10 +2558,10 @@
         <v>30</v>
       </c>
       <c r="N26" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="O26" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2566,34 +2575,34 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E27" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F27" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G27" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H27" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I27" t="s">
         <v>42</v>
       </c>
       <c r="J27" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K27" t="s">
         <v>109</v>
@@ -2605,10 +2614,10 @@
         <v>30</v>
       </c>
       <c r="N27" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="O27" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2622,28 +2631,28 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E28" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F28" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G28" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H28" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I28" t="s">
         <v>26</v>
@@ -2661,10 +2670,10 @@
         <v>30</v>
       </c>
       <c r="N28" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="O28" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
@@ -2678,28 +2687,28 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B29" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C29" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E29" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F29" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G29" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H29" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I29" t="s">
         <v>26</v>
@@ -2717,10 +2726,10 @@
         <v>30</v>
       </c>
       <c r="N29" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="O29" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2734,28 +2743,28 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C30" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E30" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F30" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G30" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H30" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I30" t="s">
         <v>26</v>
@@ -2773,10 +2782,10 @@
         <v>30</v>
       </c>
       <c r="N30" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="O30" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2790,28 +2799,28 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C31" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E31" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F31" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G31" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H31" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I31" t="s">
         <v>26</v>
@@ -2829,10 +2838,10 @@
         <v>30</v>
       </c>
       <c r="N31" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="O31" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2846,34 +2855,34 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C32" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D32" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E32" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F32" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="G32" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H32" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I32" t="s">
         <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>27</v>
+        <v>170</v>
       </c>
       <c r="K32" t="s">
         <v>28</v>
@@ -2885,10 +2894,10 @@
         <v>30</v>
       </c>
       <c r="N32" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="O32" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -2902,52 +2911,52 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B33" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E33" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F33" t="s">
-        <v>65</v>
+        <v>174</v>
       </c>
       <c r="G33" t="s">
         <v>171</v>
       </c>
       <c r="H33" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I33" t="s">
         <v>26</v>
       </c>
       <c r="J33" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K33" t="s">
         <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="M33" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="N33" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="O33" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -2958,34 +2967,34 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B34" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C34" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D34" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E34" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="F34" t="s">
         <v>65</v>
       </c>
       <c r="G34" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H34" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="I34" t="s">
         <v>26</v>
       </c>
       <c r="J34" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="K34" t="s">
         <v>28</v>
@@ -3014,52 +3023,52 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B35" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C35" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D35" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E35" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F35" t="s">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="G35" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="H35" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I35" t="s">
         <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>178</v>
+        <v>27</v>
       </c>
       <c r="K35" t="s">
         <v>28</v>
       </c>
       <c r="L35" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="M35" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="O35" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3070,28 +3079,28 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C36" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D36" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E36" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F36" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G36" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H36" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="I36" t="s">
         <v>26</v>
@@ -3103,16 +3112,16 @@
         <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="M36" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="N36" t="s">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="O36" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -3126,28 +3135,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C37" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D37" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E37" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F37" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G37" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H37" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="I37" t="s">
         <v>26</v>
@@ -3165,10 +3174,10 @@
         <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="O37" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -3182,28 +3191,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B38" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C38" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D38" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E38" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F38" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G38" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H38" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
@@ -3221,10 +3230,10 @@
         <v>30</v>
       </c>
       <c r="N38" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="O38" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3238,28 +3247,28 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C39" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D39" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E39" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F39" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G39" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H39" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
@@ -3277,10 +3286,10 @@
         <v>30</v>
       </c>
       <c r="N39" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="O39" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -3294,28 +3303,28 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B40" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C40" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D40" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E40" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F40" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G40" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H40" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
@@ -3333,10 +3342,10 @@
         <v>30</v>
       </c>
       <c r="N40" t="s">
-        <v>209</v>
+        <v>46</v>
       </c>
       <c r="O40" t="s">
-        <v>210</v>
+        <v>47</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -3345,33 +3354,33 @@
         <v>1</v>
       </c>
       <c r="R40" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C41" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D41" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E41" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F41" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G41" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H41" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
@@ -3389,10 +3398,10 @@
         <v>30</v>
       </c>
       <c r="N41" t="s">
-        <v>209</v>
+        <v>46</v>
       </c>
       <c r="O41" t="s">
-        <v>210</v>
+        <v>47</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3401,33 +3410,33 @@
         <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B42" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C42" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D42" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E42" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F42" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G42" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H42" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I42" t="s">
         <v>26</v>
@@ -3445,10 +3454,10 @@
         <v>30</v>
       </c>
       <c r="N42" t="s">
-        <v>209</v>
+        <v>46</v>
       </c>
       <c r="O42" t="s">
-        <v>210</v>
+        <v>47</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
@@ -3457,33 +3466,33 @@
         <v>1</v>
       </c>
       <c r="R42" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B43" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C43" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D43" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E43" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F43" t="s">
         <v>41</v>
       </c>
       <c r="G43" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H43" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I43" t="s">
         <v>42</v>
@@ -3518,28 +3527,28 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B44" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C44" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D44" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E44" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F44" t="s">
+        <v>225</v>
+      </c>
+      <c r="G44" t="s">
         <v>222</v>
       </c>
-      <c r="G44" t="s">
-        <v>219</v>
-      </c>
       <c r="H44" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I44" t="s">
         <v>26</v>
@@ -3569,33 +3578,33 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C45" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D45" t="s">
+        <v>228</v>
+      </c>
+      <c r="E45" t="s">
+        <v>229</v>
+      </c>
+      <c r="F45" t="s">
         <v>225</v>
       </c>
-      <c r="E45" t="s">
-        <v>226</v>
-      </c>
-      <c r="F45" t="s">
-        <v>222</v>
-      </c>
       <c r="G45" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H45" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I45" t="s">
         <v>26</v>
@@ -3613,10 +3622,10 @@
         <v>30</v>
       </c>
       <c r="N45" t="s">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="O45" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
@@ -3630,37 +3639,37 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B46" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C46" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D46" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E46" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F46" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G46" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H46" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="I46" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="J46" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="K46" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="L46" t="s">
         <v>29</v>
@@ -3669,10 +3678,10 @@
         <v>30</v>
       </c>
       <c r="N46" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="O46" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3681,42 +3690,42 @@
         <v>0</v>
       </c>
       <c r="R46" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B47" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C47" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D47" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E47" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F47" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G47" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="H47" t="s">
+        <v>243</v>
+      </c>
+      <c r="I47" t="s">
         <v>238</v>
       </c>
-      <c r="I47" t="s">
-        <v>233</v>
-      </c>
       <c r="J47" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K47" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="L47" t="s">
         <v>29</v>
@@ -3725,10 +3734,10 @@
         <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="O47" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3737,42 +3746,42 @@
         <v>0</v>
       </c>
       <c r="R47" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B48" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C48" t="s">
+        <v>232</v>
+      </c>
+      <c r="D48" t="s">
+        <v>233</v>
+      </c>
+      <c r="E48" t="s">
+        <v>234</v>
+      </c>
+      <c r="F48" t="s">
+        <v>235</v>
+      </c>
+      <c r="G48" t="s">
+        <v>244</v>
+      </c>
+      <c r="H48" t="s">
+        <v>245</v>
+      </c>
+      <c r="I48" t="s">
+        <v>238</v>
+      </c>
+      <c r="J48" t="s">
+        <v>146</v>
+      </c>
+      <c r="K48" t="s">
         <v>239</v>
-      </c>
-      <c r="D48" t="s">
-        <v>240</v>
-      </c>
-      <c r="E48" t="s">
-        <v>241</v>
-      </c>
-      <c r="F48" t="s">
-        <v>232</v>
-      </c>
-      <c r="G48" t="s">
-        <v>242</v>
-      </c>
-      <c r="H48" t="s">
-        <v>243</v>
-      </c>
-      <c r="I48" t="s">
-        <v>233</v>
-      </c>
-      <c r="J48" t="s">
-        <v>144</v>
-      </c>
-      <c r="K48" t="s">
-        <v>234</v>
       </c>
       <c r="L48" t="s">
         <v>29</v>
@@ -3781,10 +3790,10 @@
         <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="O48" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3793,42 +3802,42 @@
         <v>0</v>
       </c>
       <c r="R48" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B49" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C49" t="s">
+        <v>232</v>
+      </c>
+      <c r="D49" t="s">
+        <v>233</v>
+      </c>
+      <c r="E49" t="s">
+        <v>234</v>
+      </c>
+      <c r="F49" t="s">
+        <v>235</v>
+      </c>
+      <c r="G49" t="s">
+        <v>246</v>
+      </c>
+      <c r="H49" t="s">
+        <v>247</v>
+      </c>
+      <c r="I49" t="s">
+        <v>238</v>
+      </c>
+      <c r="J49" t="s">
+        <v>146</v>
+      </c>
+      <c r="K49" t="s">
         <v>239</v>
-      </c>
-      <c r="D49" t="s">
-        <v>240</v>
-      </c>
-      <c r="E49" t="s">
-        <v>241</v>
-      </c>
-      <c r="F49" t="s">
-        <v>232</v>
-      </c>
-      <c r="G49" t="s">
-        <v>244</v>
-      </c>
-      <c r="H49" t="s">
-        <v>245</v>
-      </c>
-      <c r="I49" t="s">
-        <v>233</v>
-      </c>
-      <c r="J49" t="s">
-        <v>144</v>
-      </c>
-      <c r="K49" t="s">
-        <v>234</v>
       </c>
       <c r="L49" t="s">
         <v>29</v>
@@ -3837,10 +3846,10 @@
         <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="O49" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3849,42 +3858,42 @@
         <v>0</v>
       </c>
       <c r="R49" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B50" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C50" t="s">
+        <v>232</v>
+      </c>
+      <c r="D50" t="s">
+        <v>233</v>
+      </c>
+      <c r="E50" t="s">
+        <v>234</v>
+      </c>
+      <c r="F50" t="s">
+        <v>235</v>
+      </c>
+      <c r="G50" t="s">
+        <v>248</v>
+      </c>
+      <c r="H50" t="s">
+        <v>249</v>
+      </c>
+      <c r="I50" t="s">
+        <v>238</v>
+      </c>
+      <c r="J50" t="s">
+        <v>146</v>
+      </c>
+      <c r="K50" t="s">
         <v>239</v>
-      </c>
-      <c r="D50" t="s">
-        <v>240</v>
-      </c>
-      <c r="E50" t="s">
-        <v>241</v>
-      </c>
-      <c r="F50" t="s">
-        <v>232</v>
-      </c>
-      <c r="G50" t="s">
-        <v>246</v>
-      </c>
-      <c r="H50" t="s">
-        <v>247</v>
-      </c>
-      <c r="I50" t="s">
-        <v>233</v>
-      </c>
-      <c r="J50" t="s">
-        <v>144</v>
-      </c>
-      <c r="K50" t="s">
-        <v>234</v>
       </c>
       <c r="L50" t="s">
         <v>29</v>
@@ -3893,10 +3902,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="O50" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3905,42 +3914,42 @@
         <v>0</v>
       </c>
       <c r="R50" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B51" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C51" t="s">
+        <v>232</v>
+      </c>
+      <c r="D51" t="s">
+        <v>233</v>
+      </c>
+      <c r="E51" t="s">
+        <v>234</v>
+      </c>
+      <c r="F51" t="s">
+        <v>235</v>
+      </c>
+      <c r="G51" t="s">
+        <v>250</v>
+      </c>
+      <c r="H51" t="s">
+        <v>251</v>
+      </c>
+      <c r="I51" t="s">
+        <v>238</v>
+      </c>
+      <c r="J51" t="s">
+        <v>146</v>
+      </c>
+      <c r="K51" t="s">
         <v>239</v>
-      </c>
-      <c r="D51" t="s">
-        <v>240</v>
-      </c>
-      <c r="E51" t="s">
-        <v>241</v>
-      </c>
-      <c r="F51" t="s">
-        <v>232</v>
-      </c>
-      <c r="G51" t="s">
-        <v>248</v>
-      </c>
-      <c r="H51" t="s">
-        <v>249</v>
-      </c>
-      <c r="I51" t="s">
-        <v>233</v>
-      </c>
-      <c r="J51" t="s">
-        <v>144</v>
-      </c>
-      <c r="K51" t="s">
-        <v>234</v>
       </c>
       <c r="L51" t="s">
         <v>29</v>
@@ -3949,10 +3958,10 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="O51" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3961,42 +3970,42 @@
         <v>0</v>
       </c>
       <c r="R51" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B52" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C52" t="s">
+        <v>232</v>
+      </c>
+      <c r="D52" t="s">
+        <v>233</v>
+      </c>
+      <c r="E52" t="s">
+        <v>234</v>
+      </c>
+      <c r="F52" t="s">
+        <v>235</v>
+      </c>
+      <c r="G52" t="s">
+        <v>252</v>
+      </c>
+      <c r="H52" t="s">
+        <v>253</v>
+      </c>
+      <c r="I52" t="s">
+        <v>238</v>
+      </c>
+      <c r="J52" t="s">
+        <v>146</v>
+      </c>
+      <c r="K52" t="s">
         <v>239</v>
-      </c>
-      <c r="D52" t="s">
-        <v>240</v>
-      </c>
-      <c r="E52" t="s">
-        <v>241</v>
-      </c>
-      <c r="F52" t="s">
-        <v>232</v>
-      </c>
-      <c r="G52" t="s">
-        <v>250</v>
-      </c>
-      <c r="H52" t="s">
-        <v>251</v>
-      </c>
-      <c r="I52" t="s">
-        <v>233</v>
-      </c>
-      <c r="J52" t="s">
-        <v>144</v>
-      </c>
-      <c r="K52" t="s">
-        <v>234</v>
       </c>
       <c r="L52" t="s">
         <v>29</v>
@@ -4005,10 +4014,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="O52" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4017,42 +4026,42 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B53" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C53" t="s">
+        <v>254</v>
+      </c>
+      <c r="D53" t="s">
+        <v>255</v>
+      </c>
+      <c r="E53" t="s">
+        <v>256</v>
+      </c>
+      <c r="F53" t="s">
+        <v>235</v>
+      </c>
+      <c r="G53" t="s">
+        <v>257</v>
+      </c>
+      <c r="H53" t="s">
+        <v>258</v>
+      </c>
+      <c r="I53" t="s">
+        <v>238</v>
+      </c>
+      <c r="J53" t="s">
+        <v>146</v>
+      </c>
+      <c r="K53" t="s">
         <v>239</v>
-      </c>
-      <c r="D53" t="s">
-        <v>240</v>
-      </c>
-      <c r="E53" t="s">
-        <v>241</v>
-      </c>
-      <c r="F53" t="s">
-        <v>232</v>
-      </c>
-      <c r="G53" t="s">
-        <v>252</v>
-      </c>
-      <c r="H53" t="s">
-        <v>253</v>
-      </c>
-      <c r="I53" t="s">
-        <v>233</v>
-      </c>
-      <c r="J53" t="s">
-        <v>144</v>
-      </c>
-      <c r="K53" t="s">
-        <v>234</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
@@ -4061,10 +4070,10 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="O53" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4073,42 +4082,42 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B54" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C54" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D54" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="E54" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="F54" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G54" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H54" t="s">
         <v>255</v>
       </c>
       <c r="I54" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="J54" t="s">
-        <v>144</v>
+        <v>27</v>
       </c>
       <c r="K54" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="L54" t="s">
         <v>29</v>
@@ -4117,10 +4126,10 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="O54" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -4129,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>236</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -734,61 +734,61 @@
     <t xml:space="preserve">null</t>
   </si>
   <si>
+    <t xml:space="preserve">2024A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High school or equivalent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">high-school</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some college or associate's degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">some-college-aa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor's degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bachelors-degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graduate or professional degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">graduate-degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High school degree or higher, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hs-plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor's degree or higher, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ba-plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total-population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of foreign-born population (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign-born</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2025-12-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High school or equivalent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">high-school</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Some college or associate's degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">some-college-aa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bachelor's degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bachelors-degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graduate or professional degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">graduate-degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High school degree or higher, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hs-plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bachelor's degree or higher, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ba-plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total-population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of foreign-born population (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foreign-born</t>
   </si>
 </sst>
 </file>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="R46" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47">
@@ -3713,10 +3713,10 @@
         <v>235</v>
       </c>
       <c r="G47" t="s">
+        <v>241</v>
+      </c>
+      <c r="H47" t="s">
         <v>242</v>
-      </c>
-      <c r="H47" t="s">
-        <v>243</v>
       </c>
       <c r="I47" t="s">
         <v>238</v>
@@ -3746,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="R47" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48">
@@ -3769,10 +3769,10 @@
         <v>235</v>
       </c>
       <c r="G48" t="s">
+        <v>243</v>
+      </c>
+      <c r="H48" t="s">
         <v>244</v>
-      </c>
-      <c r="H48" t="s">
-        <v>245</v>
       </c>
       <c r="I48" t="s">
         <v>238</v>
@@ -3802,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="R48" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49">
@@ -3825,10 +3825,10 @@
         <v>235</v>
       </c>
       <c r="G49" t="s">
+        <v>245</v>
+      </c>
+      <c r="H49" t="s">
         <v>246</v>
-      </c>
-      <c r="H49" t="s">
-        <v>247</v>
       </c>
       <c r="I49" t="s">
         <v>238</v>
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="R49" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50">
@@ -3881,10 +3881,10 @@
         <v>235</v>
       </c>
       <c r="G50" t="s">
+        <v>247</v>
+      </c>
+      <c r="H50" t="s">
         <v>248</v>
-      </c>
-      <c r="H50" t="s">
-        <v>249</v>
       </c>
       <c r="I50" t="s">
         <v>238</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="R50" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51">
@@ -3937,10 +3937,10 @@
         <v>235</v>
       </c>
       <c r="G51" t="s">
+        <v>249</v>
+      </c>
+      <c r="H51" t="s">
         <v>250</v>
-      </c>
-      <c r="H51" t="s">
-        <v>251</v>
       </c>
       <c r="I51" t="s">
         <v>238</v>
@@ -3970,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="R51" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52">
@@ -3993,10 +3993,10 @@
         <v>235</v>
       </c>
       <c r="G52" t="s">
+        <v>251</v>
+      </c>
+      <c r="H52" t="s">
         <v>252</v>
-      </c>
-      <c r="H52" t="s">
-        <v>253</v>
       </c>
       <c r="I52" t="s">
         <v>238</v>
@@ -4026,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53">
@@ -4037,22 +4037,22 @@
         <v>231</v>
       </c>
       <c r="C53" t="s">
+        <v>253</v>
+      </c>
+      <c r="D53" t="s">
         <v>254</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>255</v>
-      </c>
-      <c r="E53" t="s">
-        <v>256</v>
       </c>
       <c r="F53" t="s">
         <v>235</v>
       </c>
       <c r="G53" t="s">
+        <v>256</v>
+      </c>
+      <c r="H53" t="s">
         <v>257</v>
-      </c>
-      <c r="H53" t="s">
-        <v>258</v>
       </c>
       <c r="I53" t="s">
         <v>238</v>
@@ -4082,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54">
@@ -4093,22 +4093,22 @@
         <v>231</v>
       </c>
       <c r="C54" t="s">
+        <v>253</v>
+      </c>
+      <c r="D54" t="s">
         <v>254</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>255</v>
-      </c>
-      <c r="E54" t="s">
-        <v>256</v>
       </c>
       <c r="F54" t="s">
         <v>235</v>
       </c>
       <c r="G54" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H54" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I54" t="s">
         <v>238</v>
@@ -4126,10 +4126,10 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="O54" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">null</t>
   </si>
   <si>
-    <t xml:space="preserve">2024A1</t>
+    <t xml:space="preserve">2025A1</t>
   </si>
   <si>
     <t xml:space="preserve">High school or equivalent</t>
@@ -786,9 +786,6 @@
   </si>
   <si>
     <t xml:space="preserve">foreign-born</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025A1</t>
   </si>
 </sst>
 </file>
@@ -4126,10 +4123,10 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="O54" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">2026M8</t>
   </si>
   <si>
-    <t xml:space="preserve">DMV-2026-10-02</t>
+    <t xml:space="preserve">DMV-2026-10-04</t>
   </si>
   <si>
     <t xml:space="preserve">Private sector jobs</t>
@@ -617,12 +617,6 @@
     <t xml:space="preserve">crime-rate-total</t>
   </si>
   <si>
-    <t xml:space="preserve">2024M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M9</t>
-  </si>
-  <si>
     <t xml:space="preserve">Violent crimes</t>
   </si>
   <si>
@@ -710,16 +704,43 @@
     <t xml:space="preserve">about</t>
   </si>
   <si>
+    <t xml:space="preserve">Population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total-population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Census Bureau and Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">null</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of foreign-born population (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign-born</t>
+  </si>
+  <si>
     <t xml:space="preserve">Educational attainment</t>
   </si>
   <si>
     <t xml:space="preserve">eduatt</t>
   </si>
   <si>
-    <t xml:space="preserve">Educational attaintment for population aged 25 and older</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Census Bureau and Lightcast</t>
+    <t xml:space="preserve">Educational attainment for population aged 25 and older</t>
   </si>
   <si>
     <t xml:space="preserve">Less than high school</t>
@@ -728,15 +749,6 @@
     <t xml:space="preserve">less-than-hs</t>
   </si>
   <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025A1</t>
-  </si>
-  <si>
     <t xml:space="preserve">High school or equivalent</t>
   </si>
   <si>
@@ -771,21 +783,6 @@
   </si>
   <si>
     <t xml:space="preserve">ba-plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total-population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of foreign-born population (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foreign-born</t>
   </si>
 </sst>
 </file>
@@ -3171,10 +3168,10 @@
         <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>201</v>
+        <v>70</v>
       </c>
       <c r="O37" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -3206,10 +3203,10 @@
         <v>198</v>
       </c>
       <c r="G38" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H38" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
@@ -3227,10 +3224,10 @@
         <v>30</v>
       </c>
       <c r="N38" t="s">
-        <v>201</v>
+        <v>70</v>
       </c>
       <c r="O38" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3262,10 +3259,10 @@
         <v>198</v>
       </c>
       <c r="G39" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H39" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
@@ -3283,10 +3280,10 @@
         <v>30</v>
       </c>
       <c r="N39" t="s">
-        <v>201</v>
+        <v>70</v>
       </c>
       <c r="O39" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -3300,28 +3297,28 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>205</v>
+      </c>
+      <c r="B40" t="s">
+        <v>206</v>
+      </c>
+      <c r="C40" t="s">
         <v>207</v>
       </c>
-      <c r="B40" t="s">
+      <c r="D40" t="s">
         <v>208</v>
       </c>
-      <c r="C40" t="s">
+      <c r="E40" t="s">
         <v>209</v>
       </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>210</v>
       </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
         <v>211</v>
       </c>
-      <c r="F40" t="s">
+      <c r="H40" t="s">
         <v>212</v>
-      </c>
-      <c r="G40" t="s">
-        <v>213</v>
-      </c>
-      <c r="H40" t="s">
-        <v>214</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
@@ -3356,28 +3353,28 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" t="s">
+        <v>206</v>
+      </c>
+      <c r="C41" t="s">
         <v>207</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" t="s">
         <v>208</v>
       </c>
-      <c r="C41" t="s">
+      <c r="E41" t="s">
         <v>209</v>
       </c>
-      <c r="D41" t="s">
+      <c r="F41" t="s">
         <v>210</v>
       </c>
-      <c r="E41" t="s">
-        <v>211</v>
-      </c>
-      <c r="F41" t="s">
-        <v>212</v>
-      </c>
       <c r="G41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H41" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
@@ -3412,28 +3409,28 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>205</v>
+      </c>
+      <c r="B42" t="s">
+        <v>206</v>
+      </c>
+      <c r="C42" t="s">
         <v>207</v>
       </c>
-      <c r="B42" t="s">
+      <c r="D42" t="s">
         <v>208</v>
       </c>
-      <c r="C42" t="s">
+      <c r="E42" t="s">
         <v>209</v>
       </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
         <v>210</v>
       </c>
-      <c r="E42" t="s">
-        <v>211</v>
-      </c>
-      <c r="F42" t="s">
-        <v>212</v>
-      </c>
       <c r="G42" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I42" t="s">
         <v>26</v>
@@ -3468,28 +3465,28 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C43" t="s">
+        <v>217</v>
+      </c>
+      <c r="D43" t="s">
+        <v>218</v>
+      </c>
+      <c r="E43" t="s">
         <v>219</v>
-      </c>
-      <c r="D43" t="s">
-        <v>220</v>
-      </c>
-      <c r="E43" t="s">
-        <v>221</v>
       </c>
       <c r="F43" t="s">
         <v>41</v>
       </c>
       <c r="G43" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H43" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I43" t="s">
         <v>42</v>
@@ -3524,28 +3521,28 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B44" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C44" t="s">
+        <v>220</v>
+      </c>
+      <c r="D44" t="s">
+        <v>221</v>
+      </c>
+      <c r="E44" t="s">
         <v>222</v>
       </c>
-      <c r="D44" t="s">
+      <c r="F44" t="s">
         <v>223</v>
       </c>
-      <c r="E44" t="s">
-        <v>224</v>
-      </c>
-      <c r="F44" t="s">
-        <v>225</v>
-      </c>
       <c r="G44" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H44" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I44" t="s">
         <v>26</v>
@@ -3575,33 +3572,33 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B45" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C45" t="s">
+        <v>225</v>
+      </c>
+      <c r="D45" t="s">
+        <v>226</v>
+      </c>
+      <c r="E45" t="s">
         <v>227</v>
       </c>
-      <c r="D45" t="s">
-        <v>228</v>
-      </c>
-      <c r="E45" t="s">
-        <v>229</v>
-      </c>
       <c r="F45" t="s">
+        <v>223</v>
+      </c>
+      <c r="G45" t="s">
         <v>225</v>
       </c>
-      <c r="G45" t="s">
-        <v>227</v>
-      </c>
       <c r="H45" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I45" t="s">
         <v>26</v>
@@ -3636,37 +3633,37 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>228</v>
+      </c>
+      <c r="B46" t="s">
+        <v>229</v>
+      </c>
+      <c r="C46" t="s">
         <v>230</v>
       </c>
-      <c r="B46" t="s">
+      <c r="D46" t="s">
         <v>231</v>
       </c>
-      <c r="C46" t="s">
+      <c r="E46" t="s">
         <v>232</v>
       </c>
-      <c r="D46" t="s">
+      <c r="F46" t="s">
         <v>233</v>
       </c>
-      <c r="E46" t="s">
+      <c r="G46" t="s">
+        <v>232</v>
+      </c>
+      <c r="H46" t="s">
+        <v>231</v>
+      </c>
+      <c r="I46" t="s">
         <v>234</v>
       </c>
-      <c r="F46" t="s">
+      <c r="J46" t="s">
+        <v>27</v>
+      </c>
+      <c r="K46" t="s">
         <v>235</v>
-      </c>
-      <c r="G46" t="s">
-        <v>236</v>
-      </c>
-      <c r="H46" t="s">
-        <v>237</v>
-      </c>
-      <c r="I46" t="s">
-        <v>238</v>
-      </c>
-      <c r="J46" t="s">
-        <v>146</v>
-      </c>
-      <c r="K46" t="s">
-        <v>239</v>
       </c>
       <c r="L46" t="s">
         <v>29</v>
@@ -3675,10 +3672,10 @@
         <v>30</v>
       </c>
       <c r="N46" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O46" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3692,37 +3689,37 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>228</v>
+      </c>
+      <c r="B47" t="s">
+        <v>229</v>
+      </c>
+      <c r="C47" t="s">
         <v>230</v>
       </c>
-      <c r="B47" t="s">
+      <c r="D47" t="s">
         <v>231</v>
       </c>
-      <c r="C47" t="s">
+      <c r="E47" t="s">
         <v>232</v>
       </c>
-      <c r="D47" t="s">
+      <c r="F47" t="s">
         <v>233</v>
       </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
+        <v>238</v>
+      </c>
+      <c r="H47" t="s">
+        <v>239</v>
+      </c>
+      <c r="I47" t="s">
         <v>234</v>
-      </c>
-      <c r="F47" t="s">
-        <v>235</v>
-      </c>
-      <c r="G47" t="s">
-        <v>241</v>
-      </c>
-      <c r="H47" t="s">
-        <v>242</v>
-      </c>
-      <c r="I47" t="s">
-        <v>238</v>
       </c>
       <c r="J47" t="s">
         <v>146</v>
       </c>
       <c r="K47" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L47" t="s">
         <v>29</v>
@@ -3731,10 +3728,10 @@
         <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O47" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3748,22 +3745,22 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C48" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D48" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48" t="s">
+        <v>242</v>
+      </c>
+      <c r="F48" t="s">
         <v>233</v>
-      </c>
-      <c r="E48" t="s">
-        <v>234</v>
-      </c>
-      <c r="F48" t="s">
-        <v>235</v>
       </c>
       <c r="G48" t="s">
         <v>243</v>
@@ -3772,13 +3769,13 @@
         <v>244</v>
       </c>
       <c r="I48" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J48" t="s">
         <v>146</v>
       </c>
       <c r="K48" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L48" t="s">
         <v>29</v>
@@ -3787,10 +3784,10 @@
         <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O48" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3804,22 +3801,22 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B49" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C49" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D49" t="s">
+        <v>241</v>
+      </c>
+      <c r="E49" t="s">
+        <v>242</v>
+      </c>
+      <c r="F49" t="s">
         <v>233</v>
-      </c>
-      <c r="E49" t="s">
-        <v>234</v>
-      </c>
-      <c r="F49" t="s">
-        <v>235</v>
       </c>
       <c r="G49" t="s">
         <v>245</v>
@@ -3828,13 +3825,13 @@
         <v>246</v>
       </c>
       <c r="I49" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J49" t="s">
         <v>146</v>
       </c>
       <c r="K49" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L49" t="s">
         <v>29</v>
@@ -3843,10 +3840,10 @@
         <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O49" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3860,22 +3857,22 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B50" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C50" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E50" t="s">
+        <v>242</v>
+      </c>
+      <c r="F50" t="s">
         <v>233</v>
-      </c>
-      <c r="E50" t="s">
-        <v>234</v>
-      </c>
-      <c r="F50" t="s">
-        <v>235</v>
       </c>
       <c r="G50" t="s">
         <v>247</v>
@@ -3884,13 +3881,13 @@
         <v>248</v>
       </c>
       <c r="I50" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J50" t="s">
         <v>146</v>
       </c>
       <c r="K50" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L50" t="s">
         <v>29</v>
@@ -3899,10 +3896,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O50" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3916,22 +3913,22 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B51" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C51" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E51" t="s">
+        <v>242</v>
+      </c>
+      <c r="F51" t="s">
         <v>233</v>
-      </c>
-      <c r="E51" t="s">
-        <v>234</v>
-      </c>
-      <c r="F51" t="s">
-        <v>235</v>
       </c>
       <c r="G51" t="s">
         <v>249</v>
@@ -3940,13 +3937,13 @@
         <v>250</v>
       </c>
       <c r="I51" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J51" t="s">
         <v>146</v>
       </c>
       <c r="K51" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L51" t="s">
         <v>29</v>
@@ -3955,10 +3952,10 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O51" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3972,22 +3969,22 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B52" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C52" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D52" t="s">
+        <v>241</v>
+      </c>
+      <c r="E52" t="s">
+        <v>242</v>
+      </c>
+      <c r="F52" t="s">
         <v>233</v>
-      </c>
-      <c r="E52" t="s">
-        <v>234</v>
-      </c>
-      <c r="F52" t="s">
-        <v>235</v>
       </c>
       <c r="G52" t="s">
         <v>251</v>
@@ -3996,13 +3993,13 @@
         <v>252</v>
       </c>
       <c r="I52" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J52" t="s">
         <v>146</v>
       </c>
       <c r="K52" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L52" t="s">
         <v>29</v>
@@ -4011,10 +4008,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O52" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4028,37 +4025,37 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B53" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C53" t="s">
+        <v>240</v>
+      </c>
+      <c r="D53" t="s">
+        <v>241</v>
+      </c>
+      <c r="E53" t="s">
+        <v>242</v>
+      </c>
+      <c r="F53" t="s">
+        <v>233</v>
+      </c>
+      <c r="G53" t="s">
         <v>253</v>
       </c>
-      <c r="D53" t="s">
+      <c r="H53" t="s">
         <v>254</v>
       </c>
-      <c r="E53" t="s">
-        <v>255</v>
-      </c>
-      <c r="F53" t="s">
-        <v>235</v>
-      </c>
-      <c r="G53" t="s">
-        <v>256</v>
-      </c>
-      <c r="H53" t="s">
-        <v>257</v>
-      </c>
       <c r="I53" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J53" t="s">
         <v>146</v>
       </c>
       <c r="K53" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
@@ -4067,10 +4064,10 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O53" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4084,37 +4081,37 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B54" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C54" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="D54" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="E54" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F54" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G54" t="s">
         <v>255</v>
       </c>
       <c r="H54" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I54" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J54" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="K54" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L54" t="s">
         <v>29</v>
@@ -4123,10 +4120,10 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O54" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -732,6 +732,9 @@
   </si>
   <si>
     <t xml:space="preserve">foreign-born</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019A1</t>
   </si>
   <si>
     <t xml:space="preserve">Educational attainment</t>
@@ -3728,7 +3731,7 @@
         <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O47" t="s">
         <v>236</v>
@@ -3751,22 +3754,22 @@
         <v>229</v>
       </c>
       <c r="C48" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D48" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E48" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
       </c>
       <c r="G48" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H48" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I48" t="s">
         <v>234</v>
@@ -3784,7 +3787,7 @@
         <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O48" t="s">
         <v>236</v>
@@ -3807,22 +3810,22 @@
         <v>229</v>
       </c>
       <c r="C49" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D49" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E49" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F49" t="s">
         <v>233</v>
       </c>
       <c r="G49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I49" t="s">
         <v>234</v>
@@ -3840,7 +3843,7 @@
         <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O49" t="s">
         <v>236</v>
@@ -3863,22 +3866,22 @@
         <v>229</v>
       </c>
       <c r="C50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
       </c>
       <c r="G50" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I50" t="s">
         <v>234</v>
@@ -3896,7 +3899,7 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O50" t="s">
         <v>236</v>
@@ -3919,22 +3922,22 @@
         <v>229</v>
       </c>
       <c r="C51" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D51" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E51" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
       </c>
       <c r="G51" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H51" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I51" t="s">
         <v>234</v>
@@ -3952,7 +3955,7 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O51" t="s">
         <v>236</v>
@@ -3975,22 +3978,22 @@
         <v>229</v>
       </c>
       <c r="C52" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E52" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F52" t="s">
         <v>233</v>
       </c>
       <c r="G52" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H52" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I52" t="s">
         <v>234</v>
@@ -4008,7 +4011,7 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O52" t="s">
         <v>236</v>
@@ -4031,22 +4034,22 @@
         <v>229</v>
       </c>
       <c r="C53" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D53" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E53" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F53" t="s">
         <v>233</v>
       </c>
       <c r="G53" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H53" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I53" t="s">
         <v>234</v>
@@ -4064,7 +4067,7 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O53" t="s">
         <v>236</v>
@@ -4087,22 +4090,22 @@
         <v>229</v>
       </c>
       <c r="C54" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D54" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F54" t="s">
         <v>233</v>
       </c>
       <c r="G54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H54" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I54" t="s">
         <v>234</v>
@@ -4120,7 +4123,7 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O54" t="s">
         <v>236</v>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -717,9 +717,6 @@
   </si>
   <si>
     <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">null</t>
   </si>
   <si>
     <t xml:space="preserve">2024A1</t>
@@ -3666,7 +3663,7 @@
         <v>27</v>
       </c>
       <c r="K46" t="s">
-        <v>235</v>
+        <v>28</v>
       </c>
       <c r="L46" t="s">
         <v>29</v>
@@ -3675,10 +3672,10 @@
         <v>30</v>
       </c>
       <c r="N46" t="s">
+        <v>235</v>
+      </c>
+      <c r="O46" t="s">
         <v>236</v>
-      </c>
-      <c r="O46" t="s">
-        <v>237</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3710,10 +3707,10 @@
         <v>233</v>
       </c>
       <c r="G47" t="s">
+        <v>237</v>
+      </c>
+      <c r="H47" t="s">
         <v>238</v>
-      </c>
-      <c r="H47" t="s">
-        <v>239</v>
       </c>
       <c r="I47" t="s">
         <v>234</v>
@@ -3722,7 +3719,7 @@
         <v>146</v>
       </c>
       <c r="K47" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="L47" t="s">
         <v>29</v>
@@ -3731,10 +3728,10 @@
         <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O47" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3754,22 +3751,22 @@
         <v>229</v>
       </c>
       <c r="C48" t="s">
+        <v>240</v>
+      </c>
+      <c r="D48" t="s">
         <v>241</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>242</v>
-      </c>
-      <c r="E48" t="s">
-        <v>243</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
       </c>
       <c r="G48" t="s">
+        <v>243</v>
+      </c>
+      <c r="H48" t="s">
         <v>244</v>
-      </c>
-      <c r="H48" t="s">
-        <v>245</v>
       </c>
       <c r="I48" t="s">
         <v>234</v>
@@ -3778,7 +3775,7 @@
         <v>146</v>
       </c>
       <c r="K48" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="L48" t="s">
         <v>29</v>
@@ -3787,10 +3784,10 @@
         <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O48" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3810,22 +3807,22 @@
         <v>229</v>
       </c>
       <c r="C49" t="s">
+        <v>240</v>
+      </c>
+      <c r="D49" t="s">
         <v>241</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>242</v>
-      </c>
-      <c r="E49" t="s">
-        <v>243</v>
       </c>
       <c r="F49" t="s">
         <v>233</v>
       </c>
       <c r="G49" t="s">
+        <v>245</v>
+      </c>
+      <c r="H49" t="s">
         <v>246</v>
-      </c>
-      <c r="H49" t="s">
-        <v>247</v>
       </c>
       <c r="I49" t="s">
         <v>234</v>
@@ -3834,7 +3831,7 @@
         <v>146</v>
       </c>
       <c r="K49" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="L49" t="s">
         <v>29</v>
@@ -3843,10 +3840,10 @@
         <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O49" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3866,22 +3863,22 @@
         <v>229</v>
       </c>
       <c r="C50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D50" t="s">
         <v>241</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>242</v>
-      </c>
-      <c r="E50" t="s">
-        <v>243</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
       </c>
       <c r="G50" t="s">
+        <v>247</v>
+      </c>
+      <c r="H50" t="s">
         <v>248</v>
-      </c>
-      <c r="H50" t="s">
-        <v>249</v>
       </c>
       <c r="I50" t="s">
         <v>234</v>
@@ -3890,7 +3887,7 @@
         <v>146</v>
       </c>
       <c r="K50" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="L50" t="s">
         <v>29</v>
@@ -3899,10 +3896,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O50" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3922,22 +3919,22 @@
         <v>229</v>
       </c>
       <c r="C51" t="s">
+        <v>240</v>
+      </c>
+      <c r="D51" t="s">
         <v>241</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>242</v>
-      </c>
-      <c r="E51" t="s">
-        <v>243</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
       </c>
       <c r="G51" t="s">
+        <v>249</v>
+      </c>
+      <c r="H51" t="s">
         <v>250</v>
-      </c>
-      <c r="H51" t="s">
-        <v>251</v>
       </c>
       <c r="I51" t="s">
         <v>234</v>
@@ -3946,7 +3943,7 @@
         <v>146</v>
       </c>
       <c r="K51" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="L51" t="s">
         <v>29</v>
@@ -3955,10 +3952,10 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O51" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3978,22 +3975,22 @@
         <v>229</v>
       </c>
       <c r="C52" t="s">
+        <v>240</v>
+      </c>
+      <c r="D52" t="s">
         <v>241</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>242</v>
-      </c>
-      <c r="E52" t="s">
-        <v>243</v>
       </c>
       <c r="F52" t="s">
         <v>233</v>
       </c>
       <c r="G52" t="s">
+        <v>251</v>
+      </c>
+      <c r="H52" t="s">
         <v>252</v>
-      </c>
-      <c r="H52" t="s">
-        <v>253</v>
       </c>
       <c r="I52" t="s">
         <v>234</v>
@@ -4002,7 +3999,7 @@
         <v>146</v>
       </c>
       <c r="K52" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="L52" t="s">
         <v>29</v>
@@ -4011,10 +4008,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O52" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4034,22 +4031,22 @@
         <v>229</v>
       </c>
       <c r="C53" t="s">
+        <v>240</v>
+      </c>
+      <c r="D53" t="s">
         <v>241</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>242</v>
-      </c>
-      <c r="E53" t="s">
-        <v>243</v>
       </c>
       <c r="F53" t="s">
         <v>233</v>
       </c>
       <c r="G53" t="s">
+        <v>253</v>
+      </c>
+      <c r="H53" t="s">
         <v>254</v>
-      </c>
-      <c r="H53" t="s">
-        <v>255</v>
       </c>
       <c r="I53" t="s">
         <v>234</v>
@@ -4058,7 +4055,7 @@
         <v>146</v>
       </c>
       <c r="K53" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
@@ -4067,10 +4064,10 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O53" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4090,22 +4087,22 @@
         <v>229</v>
       </c>
       <c r="C54" t="s">
+        <v>240</v>
+      </c>
+      <c r="D54" t="s">
         <v>241</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>242</v>
-      </c>
-      <c r="E54" t="s">
-        <v>243</v>
       </c>
       <c r="F54" t="s">
         <v>233</v>
       </c>
       <c r="G54" t="s">
+        <v>255</v>
+      </c>
+      <c r="H54" t="s">
         <v>256</v>
-      </c>
-      <c r="H54" t="s">
-        <v>257</v>
       </c>
       <c r="I54" t="s">
         <v>234</v>
@@ -4114,7 +4111,7 @@
         <v>146</v>
       </c>
       <c r="K54" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="L54" t="s">
         <v>29</v>
@@ -4123,10 +4120,10 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O54" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">2026M8</t>
   </si>
   <si>
-    <t xml:space="preserve">DMV-2026-10-04</t>
+    <t xml:space="preserve">DMV-2026-10-05</t>
   </si>
   <si>
     <t xml:space="preserve">Private sector jobs</t>
@@ -686,7 +686,10 @@
     <t xml:space="preserve">State agency reporting</t>
   </si>
   <si>
-    <t xml:space="preserve">DMV-2026-06-04</t>
+    <t xml:space="preserve">2024M11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M11</t>
   </si>
   <si>
     <t xml:space="preserve">SNAP participation</t>
@@ -3560,10 +3563,10 @@
         <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>55</v>
+        <v>224</v>
       </c>
       <c r="O44" t="s">
-        <v>56</v>
+        <v>225</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3572,7 +3575,7 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>224</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45">
@@ -3583,22 +3586,22 @@
         <v>206</v>
       </c>
       <c r="C45" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D45" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E45" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F45" t="s">
         <v>223</v>
       </c>
       <c r="G45" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H45" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I45" t="s">
         <v>26</v>
@@ -3633,31 +3636,31 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B46" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C46" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D46" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E46" t="s">
+        <v>233</v>
+      </c>
+      <c r="F46" t="s">
+        <v>234</v>
+      </c>
+      <c r="G46" t="s">
+        <v>233</v>
+      </c>
+      <c r="H46" t="s">
         <v>232</v>
       </c>
-      <c r="F46" t="s">
-        <v>233</v>
-      </c>
-      <c r="G46" t="s">
-        <v>232</v>
-      </c>
-      <c r="H46" t="s">
-        <v>231</v>
-      </c>
       <c r="I46" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J46" t="s">
         <v>27</v>
@@ -3672,10 +3675,10 @@
         <v>30</v>
       </c>
       <c r="N46" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O46" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3689,31 +3692,31 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B47" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C47" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D47" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E47" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F47" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G47" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H47" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I47" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J47" t="s">
         <v>146</v>
@@ -3728,10 +3731,10 @@
         <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O47" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3745,31 +3748,31 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B48" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C48" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D48" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E48" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F48" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G48" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H48" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I48" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J48" t="s">
         <v>146</v>
@@ -3784,10 +3787,10 @@
         <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O48" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3801,31 +3804,31 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B49" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C49" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D49" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E49" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J49" t="s">
         <v>146</v>
@@ -3840,10 +3843,10 @@
         <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3857,31 +3860,31 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B50" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G50" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J50" t="s">
         <v>146</v>
@@ -3896,10 +3899,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O50" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3913,31 +3916,31 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B51" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C51" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D51" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E51" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F51" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G51" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H51" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J51" t="s">
         <v>146</v>
@@ -3952,10 +3955,10 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O51" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3969,31 +3972,31 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B52" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C52" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E52" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F52" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G52" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H52" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I52" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J52" t="s">
         <v>146</v>
@@ -4008,10 +4011,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O52" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4025,31 +4028,31 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B53" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C53" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D53" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E53" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F53" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G53" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H53" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I53" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J53" t="s">
         <v>146</v>
@@ -4064,10 +4067,10 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O53" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4081,31 +4084,31 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B54" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C54" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D54" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F54" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H54" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I54" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J54" t="s">
         <v>146</v>
@@ -4120,10 +4123,10 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O54" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -684,12 +684,6 @@
   </si>
   <si>
     <t xml:space="preserve">State agency reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M11</t>
   </si>
   <si>
     <t xml:space="preserve">SNAP participation</t>
@@ -3563,10 +3557,10 @@
         <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>224</v>
+        <v>55</v>
       </c>
       <c r="O44" t="s">
-        <v>225</v>
+        <v>56</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3586,22 +3580,22 @@
         <v>206</v>
       </c>
       <c r="C45" t="s">
+        <v>224</v>
+      </c>
+      <c r="D45" t="s">
+        <v>225</v>
+      </c>
+      <c r="E45" t="s">
         <v>226</v>
-      </c>
-      <c r="D45" t="s">
-        <v>227</v>
-      </c>
-      <c r="E45" t="s">
-        <v>228</v>
       </c>
       <c r="F45" t="s">
         <v>223</v>
       </c>
       <c r="G45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H45" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I45" t="s">
         <v>26</v>
@@ -3636,31 +3630,31 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>227</v>
+      </c>
+      <c r="B46" t="s">
+        <v>228</v>
+      </c>
+      <c r="C46" t="s">
         <v>229</v>
       </c>
-      <c r="B46" t="s">
+      <c r="D46" t="s">
         <v>230</v>
       </c>
-      <c r="C46" t="s">
+      <c r="E46" t="s">
         <v>231</v>
       </c>
-      <c r="D46" t="s">
+      <c r="F46" t="s">
         <v>232</v>
       </c>
-      <c r="E46" t="s">
+      <c r="G46" t="s">
+        <v>231</v>
+      </c>
+      <c r="H46" t="s">
+        <v>230</v>
+      </c>
+      <c r="I46" t="s">
         <v>233</v>
-      </c>
-      <c r="F46" t="s">
-        <v>234</v>
-      </c>
-      <c r="G46" t="s">
-        <v>233</v>
-      </c>
-      <c r="H46" t="s">
-        <v>232</v>
-      </c>
-      <c r="I46" t="s">
-        <v>235</v>
       </c>
       <c r="J46" t="s">
         <v>27</v>
@@ -3675,10 +3669,10 @@
         <v>30</v>
       </c>
       <c r="N46" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="O46" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3692,31 +3686,31 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C47" t="s">
         <v>229</v>
       </c>
-      <c r="B47" t="s">
+      <c r="D47" t="s">
         <v>230</v>
       </c>
-      <c r="C47" t="s">
+      <c r="E47" t="s">
         <v>231</v>
       </c>
-      <c r="D47" t="s">
+      <c r="F47" t="s">
         <v>232</v>
       </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
+        <v>236</v>
+      </c>
+      <c r="H47" t="s">
+        <v>237</v>
+      </c>
+      <c r="I47" t="s">
         <v>233</v>
-      </c>
-      <c r="F47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G47" t="s">
-        <v>238</v>
-      </c>
-      <c r="H47" t="s">
-        <v>239</v>
-      </c>
-      <c r="I47" t="s">
-        <v>235</v>
       </c>
       <c r="J47" t="s">
         <v>146</v>
@@ -3731,10 +3725,10 @@
         <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3748,31 +3742,31 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C48" t="s">
+        <v>239</v>
+      </c>
+      <c r="D48" t="s">
+        <v>240</v>
+      </c>
+      <c r="E48" t="s">
         <v>241</v>
       </c>
-      <c r="D48" t="s">
+      <c r="F48" t="s">
+        <v>232</v>
+      </c>
+      <c r="G48" t="s">
         <v>242</v>
       </c>
-      <c r="E48" t="s">
+      <c r="H48" t="s">
         <v>243</v>
       </c>
-      <c r="F48" t="s">
-        <v>234</v>
-      </c>
-      <c r="G48" t="s">
-        <v>244</v>
-      </c>
-      <c r="H48" t="s">
-        <v>245</v>
-      </c>
       <c r="I48" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J48" t="s">
         <v>146</v>
@@ -3787,10 +3781,10 @@
         <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O48" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3804,31 +3798,31 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B49" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C49" t="s">
+        <v>239</v>
+      </c>
+      <c r="D49" t="s">
+        <v>240</v>
+      </c>
+      <c r="E49" t="s">
         <v>241</v>
       </c>
-      <c r="D49" t="s">
-        <v>242</v>
-      </c>
-      <c r="E49" t="s">
-        <v>243</v>
-      </c>
       <c r="F49" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G49" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H49" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I49" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J49" t="s">
         <v>146</v>
@@ -3843,10 +3837,10 @@
         <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O49" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3860,31 +3854,31 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B50" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C50" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" t="s">
+        <v>240</v>
+      </c>
+      <c r="E50" t="s">
         <v>241</v>
       </c>
-      <c r="D50" t="s">
-        <v>242</v>
-      </c>
-      <c r="E50" t="s">
-        <v>243</v>
-      </c>
       <c r="F50" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G50" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H50" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I50" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J50" t="s">
         <v>146</v>
@@ -3899,10 +3893,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O50" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3916,31 +3910,31 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
+        <v>239</v>
+      </c>
+      <c r="D51" t="s">
+        <v>240</v>
+      </c>
+      <c r="E51" t="s">
         <v>241</v>
       </c>
-      <c r="D51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E51" t="s">
-        <v>243</v>
-      </c>
       <c r="F51" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G51" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H51" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I51" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J51" t="s">
         <v>146</v>
@@ -3955,10 +3949,10 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O51" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3972,31 +3966,31 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B52" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C52" t="s">
+        <v>239</v>
+      </c>
+      <c r="D52" t="s">
+        <v>240</v>
+      </c>
+      <c r="E52" t="s">
         <v>241</v>
       </c>
-      <c r="D52" t="s">
-        <v>242</v>
-      </c>
-      <c r="E52" t="s">
-        <v>243</v>
-      </c>
       <c r="F52" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G52" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H52" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I52" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J52" t="s">
         <v>146</v>
@@ -4011,10 +4005,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O52" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4028,31 +4022,31 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B53" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C53" t="s">
+        <v>239</v>
+      </c>
+      <c r="D53" t="s">
+        <v>240</v>
+      </c>
+      <c r="E53" t="s">
         <v>241</v>
       </c>
-      <c r="D53" t="s">
-        <v>242</v>
-      </c>
-      <c r="E53" t="s">
-        <v>243</v>
-      </c>
       <c r="F53" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G53" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H53" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I53" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J53" t="s">
         <v>146</v>
@@ -4067,10 +4061,10 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4084,31 +4078,31 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B54" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C54" t="s">
+        <v>239</v>
+      </c>
+      <c r="D54" t="s">
+        <v>240</v>
+      </c>
+      <c r="E54" t="s">
         <v>241</v>
       </c>
-      <c r="D54" t="s">
-        <v>242</v>
-      </c>
-      <c r="E54" t="s">
-        <v>243</v>
-      </c>
       <c r="F54" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G54" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H54" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I54" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J54" t="s">
         <v>146</v>
@@ -4123,10 +4117,10 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O54" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -113,7 +113,7 @@
     <t xml:space="preserve">2026M8</t>
   </si>
   <si>
-    <t xml:space="preserve">DMV-2026-10-05</t>
+    <t xml:space="preserve">DMV-2026-10-06</t>
   </si>
   <si>
     <t xml:space="preserve">Private sector jobs</t>
@@ -3171,7 +3171,7 @@
         <v>71</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
@@ -3227,7 +3227,7 @@
         <v>71</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
         <v>71</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
@@ -3557,10 +3557,10 @@
         <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="O44" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="252">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">2026M8</t>
   </si>
   <si>
-    <t xml:space="preserve">DMV-2026-10-06</t>
+    <t xml:space="preserve">DMV-2026-10-07</t>
   </si>
   <si>
     <t xml:space="preserve">Private sector jobs</t>
@@ -513,18 +513,6 @@
   </si>
   <si>
     <t xml:space="preserve">destination-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue per available room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotel-revpar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.[00]</t>
   </si>
   <si>
     <t xml:space="preserve">Total air passengers served</t>
@@ -1933,10 +1921,10 @@
         <v>69</v>
       </c>
       <c r="N15" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="O15" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -2861,19 +2849,19 @@
         <v>169</v>
       </c>
       <c r="F32" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="G32" t="s">
         <v>167</v>
       </c>
       <c r="H32" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I32" t="s">
         <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>170</v>
+        <v>27</v>
       </c>
       <c r="K32" t="s">
         <v>28</v>
@@ -2885,10 +2873,10 @@
         <v>30</v>
       </c>
       <c r="N32" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="O32" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -2908,46 +2896,46 @@
         <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D33" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E33" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F33" t="s">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="G33" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="H33" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I33" t="s">
         <v>26</v>
       </c>
       <c r="J33" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="K33" t="s">
         <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="M33" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="N33" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="O33" t="s">
-        <v>177</v>
+        <v>71</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -2964,28 +2952,28 @@
         <v>166</v>
       </c>
       <c r="C34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D34" t="s">
+        <v>180</v>
+      </c>
+      <c r="E34" t="s">
         <v>179</v>
-      </c>
-      <c r="E34" t="s">
-        <v>180</v>
       </c>
       <c r="F34" t="s">
         <v>65</v>
       </c>
       <c r="G34" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H34" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I34" t="s">
         <v>26</v>
       </c>
       <c r="J34" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K34" t="s">
         <v>28</v>
@@ -3014,10 +3002,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="C35" t="s">
         <v>183</v>
@@ -3026,40 +3014,40 @@
         <v>184</v>
       </c>
       <c r="E35" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>186</v>
       </c>
       <c r="G35" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H35" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="I35" t="s">
         <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="K35" t="s">
         <v>28</v>
       </c>
       <c r="L35" t="s">
-        <v>68</v>
+        <v>189</v>
       </c>
       <c r="M35" t="s">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="N35" t="s">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="O35" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3070,55 +3058,55 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B36" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C36" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D36" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E36" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F36" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G36" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H36" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I36" t="s">
         <v>26</v>
       </c>
       <c r="J36" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="K36" t="s">
         <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="M36" t="s">
-        <v>194</v>
+        <v>30</v>
       </c>
       <c r="N36" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="O36" t="s">
-        <v>177</v>
+        <v>71</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="s">
         <v>33</v>
@@ -3126,28 +3114,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C37" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D37" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E37" t="s">
+        <v>193</v>
+      </c>
+      <c r="F37" t="s">
+        <v>194</v>
+      </c>
+      <c r="G37" t="s">
         <v>197</v>
       </c>
-      <c r="F37" t="s">
+      <c r="H37" t="s">
         <v>198</v>
-      </c>
-      <c r="G37" t="s">
-        <v>199</v>
-      </c>
-      <c r="H37" t="s">
-        <v>200</v>
       </c>
       <c r="I37" t="s">
         <v>26</v>
@@ -3182,28 +3170,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B38" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C38" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D38" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E38" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F38" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G38" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H38" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
@@ -3238,37 +3226,37 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="B39" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="C39" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D39" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E39" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="F39" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G39" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H39" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="K39" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L39" t="s">
         <v>29</v>
@@ -3277,13 +3265,13 @@
         <v>30</v>
       </c>
       <c r="N39" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="O39" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
@@ -3294,28 +3282,28 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>201</v>
+      </c>
+      <c r="B40" t="s">
+        <v>202</v>
+      </c>
+      <c r="C40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D40" t="s">
+        <v>204</v>
+      </c>
+      <c r="E40" t="s">
         <v>205</v>
       </c>
-      <c r="B40" t="s">
+      <c r="F40" t="s">
         <v>206</v>
       </c>
-      <c r="C40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D40" t="s">
-        <v>208</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
         <v>209</v>
       </c>
-      <c r="F40" t="s">
+      <c r="H40" t="s">
         <v>210</v>
-      </c>
-      <c r="G40" t="s">
-        <v>211</v>
-      </c>
-      <c r="H40" t="s">
-        <v>212</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
@@ -3350,28 +3338,28 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" t="s">
+        <v>202</v>
+      </c>
+      <c r="C41" t="s">
+        <v>203</v>
+      </c>
+      <c r="D41" t="s">
+        <v>204</v>
+      </c>
+      <c r="E41" t="s">
         <v>205</v>
       </c>
-      <c r="B41" t="s">
+      <c r="F41" t="s">
         <v>206</v>
       </c>
-      <c r="C41" t="s">
-        <v>207</v>
-      </c>
-      <c r="D41" t="s">
-        <v>208</v>
-      </c>
-      <c r="E41" t="s">
-        <v>209</v>
-      </c>
-      <c r="F41" t="s">
-        <v>210</v>
-      </c>
       <c r="G41" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
@@ -3406,43 +3394,43 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C42" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D42" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E42" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F42" t="s">
-        <v>210</v>
+        <v>41</v>
       </c>
       <c r="G42" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H42" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I42" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J42" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="K42" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="L42" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="M42" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N42" t="s">
         <v>46</v>
@@ -3462,49 +3450,49 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B43" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C43" t="s">
+        <v>216</v>
+      </c>
+      <c r="D43" t="s">
         <v>217</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>218</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>219</v>
       </c>
-      <c r="F43" t="s">
-        <v>41</v>
-      </c>
       <c r="G43" t="s">
+        <v>216</v>
+      </c>
+      <c r="H43" t="s">
         <v>217</v>
       </c>
-      <c r="H43" t="s">
-        <v>218</v>
-      </c>
       <c r="I43" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J43" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="K43" t="s">
         <v>28</v>
       </c>
       <c r="L43" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M43" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N43" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="O43" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
@@ -3518,10 +3506,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B44" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C44" t="s">
         <v>220</v>
@@ -3533,7 +3521,7 @@
         <v>222</v>
       </c>
       <c r="F44" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G44" t="s">
         <v>220</v>
@@ -3557,10 +3545,10 @@
         <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="O44" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3574,31 +3562,31 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B45" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="C45" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D45" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E45" t="s">
+        <v>227</v>
+      </c>
+      <c r="F45" t="s">
+        <v>228</v>
+      </c>
+      <c r="G45" t="s">
+        <v>227</v>
+      </c>
+      <c r="H45" t="s">
         <v>226</v>
       </c>
-      <c r="F45" t="s">
-        <v>223</v>
-      </c>
-      <c r="G45" t="s">
-        <v>224</v>
-      </c>
-      <c r="H45" t="s">
-        <v>225</v>
-      </c>
       <c r="I45" t="s">
-        <v>26</v>
+        <v>229</v>
       </c>
       <c r="J45" t="s">
         <v>27</v>
@@ -3613,16 +3601,16 @@
         <v>30</v>
       </c>
       <c r="N45" t="s">
-        <v>176</v>
+        <v>230</v>
       </c>
       <c r="O45" t="s">
-        <v>177</v>
+        <v>231</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="s">
         <v>33</v>
@@ -3630,37 +3618,37 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>223</v>
+      </c>
+      <c r="B46" t="s">
+        <v>224</v>
+      </c>
+      <c r="C46" t="s">
+        <v>225</v>
+      </c>
+      <c r="D46" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" t="s">
         <v>227</v>
       </c>
-      <c r="B46" t="s">
+      <c r="F46" t="s">
         <v>228</v>
       </c>
-      <c r="C46" t="s">
+      <c r="G46" t="s">
+        <v>232</v>
+      </c>
+      <c r="H46" t="s">
+        <v>233</v>
+      </c>
+      <c r="I46" t="s">
         <v>229</v>
       </c>
-      <c r="D46" t="s">
-        <v>230</v>
-      </c>
-      <c r="E46" t="s">
-        <v>231</v>
-      </c>
-      <c r="F46" t="s">
-        <v>232</v>
-      </c>
-      <c r="G46" t="s">
-        <v>231</v>
-      </c>
-      <c r="H46" t="s">
-        <v>230</v>
-      </c>
-      <c r="I46" t="s">
-        <v>233</v>
-      </c>
       <c r="J46" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="K46" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L46" t="s">
         <v>29</v>
@@ -3672,7 +3660,7 @@
         <v>234</v>
       </c>
       <c r="O46" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3686,31 +3674,31 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B47" t="s">
+        <v>224</v>
+      </c>
+      <c r="C47" t="s">
+        <v>235</v>
+      </c>
+      <c r="D47" t="s">
+        <v>236</v>
+      </c>
+      <c r="E47" t="s">
+        <v>237</v>
+      </c>
+      <c r="F47" t="s">
         <v>228</v>
       </c>
-      <c r="C47" t="s">
+      <c r="G47" t="s">
+        <v>238</v>
+      </c>
+      <c r="H47" t="s">
+        <v>239</v>
+      </c>
+      <c r="I47" t="s">
         <v>229</v>
-      </c>
-      <c r="D47" t="s">
-        <v>230</v>
-      </c>
-      <c r="E47" t="s">
-        <v>231</v>
-      </c>
-      <c r="F47" t="s">
-        <v>232</v>
-      </c>
-      <c r="G47" t="s">
-        <v>236</v>
-      </c>
-      <c r="H47" t="s">
-        <v>237</v>
-      </c>
-      <c r="I47" t="s">
-        <v>233</v>
       </c>
       <c r="J47" t="s">
         <v>146</v>
@@ -3725,10 +3713,10 @@
         <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O47" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3742,31 +3730,31 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s">
+        <v>224</v>
+      </c>
+      <c r="C48" t="s">
+        <v>235</v>
+      </c>
+      <c r="D48" t="s">
+        <v>236</v>
+      </c>
+      <c r="E48" t="s">
+        <v>237</v>
+      </c>
+      <c r="F48" t="s">
         <v>228</v>
       </c>
-      <c r="C48" t="s">
-        <v>239</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="G48" t="s">
         <v>240</v>
       </c>
-      <c r="E48" t="s">
+      <c r="H48" t="s">
         <v>241</v>
       </c>
-      <c r="F48" t="s">
-        <v>232</v>
-      </c>
-      <c r="G48" t="s">
-        <v>242</v>
-      </c>
-      <c r="H48" t="s">
-        <v>243</v>
-      </c>
       <c r="I48" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J48" t="s">
         <v>146</v>
@@ -3781,10 +3769,10 @@
         <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O48" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3798,31 +3786,31 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B49" t="s">
+        <v>224</v>
+      </c>
+      <c r="C49" t="s">
+        <v>235</v>
+      </c>
+      <c r="D49" t="s">
+        <v>236</v>
+      </c>
+      <c r="E49" t="s">
+        <v>237</v>
+      </c>
+      <c r="F49" t="s">
         <v>228</v>
       </c>
-      <c r="C49" t="s">
-        <v>239</v>
-      </c>
-      <c r="D49" t="s">
-        <v>240</v>
-      </c>
-      <c r="E49" t="s">
-        <v>241</v>
-      </c>
-      <c r="F49" t="s">
-        <v>232</v>
-      </c>
       <c r="G49" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H49" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I49" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J49" t="s">
         <v>146</v>
@@ -3837,10 +3825,10 @@
         <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O49" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3854,31 +3842,31 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B50" t="s">
+        <v>224</v>
+      </c>
+      <c r="C50" t="s">
+        <v>235</v>
+      </c>
+      <c r="D50" t="s">
+        <v>236</v>
+      </c>
+      <c r="E50" t="s">
+        <v>237</v>
+      </c>
+      <c r="F50" t="s">
         <v>228</v>
       </c>
-      <c r="C50" t="s">
-        <v>239</v>
-      </c>
-      <c r="D50" t="s">
-        <v>240</v>
-      </c>
-      <c r="E50" t="s">
-        <v>241</v>
-      </c>
-      <c r="F50" t="s">
-        <v>232</v>
-      </c>
       <c r="G50" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H50" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I50" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J50" t="s">
         <v>146</v>
@@ -3893,10 +3881,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O50" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3910,31 +3898,31 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B51" t="s">
+        <v>224</v>
+      </c>
+      <c r="C51" t="s">
+        <v>235</v>
+      </c>
+      <c r="D51" t="s">
+        <v>236</v>
+      </c>
+      <c r="E51" t="s">
+        <v>237</v>
+      </c>
+      <c r="F51" t="s">
         <v>228</v>
       </c>
-      <c r="C51" t="s">
-        <v>239</v>
-      </c>
-      <c r="D51" t="s">
-        <v>240</v>
-      </c>
-      <c r="E51" t="s">
-        <v>241</v>
-      </c>
-      <c r="F51" t="s">
-        <v>232</v>
-      </c>
       <c r="G51" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H51" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I51" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J51" t="s">
         <v>146</v>
@@ -3949,10 +3937,10 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O51" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3966,31 +3954,31 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B52" t="s">
+        <v>224</v>
+      </c>
+      <c r="C52" t="s">
+        <v>235</v>
+      </c>
+      <c r="D52" t="s">
+        <v>236</v>
+      </c>
+      <c r="E52" t="s">
+        <v>237</v>
+      </c>
+      <c r="F52" t="s">
         <v>228</v>
       </c>
-      <c r="C52" t="s">
-        <v>239</v>
-      </c>
-      <c r="D52" t="s">
-        <v>240</v>
-      </c>
-      <c r="E52" t="s">
-        <v>241</v>
-      </c>
-      <c r="F52" t="s">
-        <v>232</v>
-      </c>
       <c r="G52" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H52" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I52" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J52" t="s">
         <v>146</v>
@@ -4005,10 +3993,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O52" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4022,31 +4010,31 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B53" t="s">
+        <v>224</v>
+      </c>
+      <c r="C53" t="s">
+        <v>235</v>
+      </c>
+      <c r="D53" t="s">
+        <v>236</v>
+      </c>
+      <c r="E53" t="s">
+        <v>237</v>
+      </c>
+      <c r="F53" t="s">
         <v>228</v>
       </c>
-      <c r="C53" t="s">
-        <v>239</v>
-      </c>
-      <c r="D53" t="s">
-        <v>240</v>
-      </c>
-      <c r="E53" t="s">
-        <v>241</v>
-      </c>
-      <c r="F53" t="s">
-        <v>232</v>
-      </c>
       <c r="G53" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H53" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I53" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J53" t="s">
         <v>146</v>
@@ -4061,10 +4049,10 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O53" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4073,62 +4061,6 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>227</v>
-      </c>
-      <c r="B54" t="s">
-        <v>228</v>
-      </c>
-      <c r="C54" t="s">
-        <v>239</v>
-      </c>
-      <c r="D54" t="s">
-        <v>240</v>
-      </c>
-      <c r="E54" t="s">
-        <v>241</v>
-      </c>
-      <c r="F54" t="s">
-        <v>232</v>
-      </c>
-      <c r="G54" t="s">
-        <v>254</v>
-      </c>
-      <c r="H54" t="s">
-        <v>255</v>
-      </c>
-      <c r="I54" t="s">
-        <v>233</v>
-      </c>
-      <c r="J54" t="s">
-        <v>146</v>
-      </c>
-      <c r="K54" t="s">
-        <v>109</v>
-      </c>
-      <c r="L54" t="s">
-        <v>29</v>
-      </c>
-      <c r="M54" t="s">
-        <v>30</v>
-      </c>
-      <c r="N54" t="s">
-        <v>238</v>
-      </c>
-      <c r="O54" t="s">
-        <v>234</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="s">
         <v>33</v>
       </c>
     </row>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -224,265 +224,265 @@
     <t xml:space="preserve">rolling-3-mean</t>
   </si>
   <si>
+    <t xml:space="preserve">Consumer prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpi-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research-hd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding obligated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States Patent and Trademark Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patent applications filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents-filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crunchbase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital volume ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor Market &amp; Workforce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">labor-market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct_diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, white workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-white</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, black workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, workers of color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-poc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, men</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-fte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internship postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-internships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mass layoff notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warn-notices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WarnTracker.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate &amp; Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real-estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial occupancy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoStar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied office space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied retail space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home-sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median sale price per square foot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mspsq</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024M5</t>
   </si>
   <si>
     <t xml:space="preserve">2026M5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpi-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">research-hd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding obligated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States Patent and Trademark Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patent applications filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents-filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crunchbase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital volume ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor Market &amp; Workforce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labor-market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct_diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, white workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-white</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, black workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, workers of color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-poc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-fte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internship postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-internships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mass layoff notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warn-notices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WarnTracker.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate &amp; Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real-estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial occupancy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoStar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied office space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied retail space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home-sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median sale price per square foot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mspsq</t>
   </si>
   <si>
     <t xml:space="preserve">Median days on market</t>
@@ -1585,10 +1585,10 @@
         <v>69</v>
       </c>
       <c r="N9" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1608,28 +1608,28 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" t="s">
         <v>72</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>73</v>
       </c>
-      <c r="E10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" t="s">
-        <v>75</v>
-      </c>
       <c r="G10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K10" t="s">
         <v>28</v>
@@ -1641,10 +1641,10 @@
         <v>30</v>
       </c>
       <c r="N10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1658,28 +1658,28 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" t="s">
         <v>79</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>80</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" t="s">
-        <v>83</v>
       </c>
       <c r="F11" t="s">
         <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
@@ -1714,28 +1714,28 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" t="s">
         <v>85</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>86</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>87</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>88</v>
-      </c>
-      <c r="G12" t="s">
-        <v>89</v>
-      </c>
-      <c r="H12" t="s">
-        <v>90</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
@@ -1753,10 +1753,10 @@
         <v>45</v>
       </c>
       <c r="N12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
@@ -1770,28 +1770,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" t="s">
         <v>93</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>94</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>95</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
         <v>96</v>
-      </c>
-      <c r="G13" t="s">
-        <v>97</v>
-      </c>
-      <c r="H13" t="s">
-        <v>98</v>
       </c>
       <c r="I13" t="s">
         <v>26</v>
@@ -1809,10 +1809,10 @@
         <v>45</v>
       </c>
       <c r="N13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1826,28 +1826,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" t="s">
         <v>93</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>94</v>
       </c>
-      <c r="E14" t="s">
-        <v>95</v>
-      </c>
-      <c r="F14" t="s">
-        <v>96</v>
-      </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I14" t="s">
         <v>26</v>
@@ -1865,10 +1865,10 @@
         <v>45</v>
       </c>
       <c r="N14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1882,37 +1882,37 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" t="s">
         <v>101</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>102</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>103</v>
-      </c>
-      <c r="D15" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" t="s">
-        <v>105</v>
       </c>
       <c r="F15" t="s">
         <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I15" t="s">
         <v>26</v>
       </c>
       <c r="J15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s">
         <v>68</v>
@@ -1938,37 +1938,37 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" t="s">
         <v>101</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
         <v>102</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>103</v>
-      </c>
-      <c r="D16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" t="s">
-        <v>105</v>
       </c>
       <c r="F16" t="s">
         <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I16" t="s">
         <v>26</v>
       </c>
       <c r="J16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s">
         <v>68</v>
@@ -1977,10 +1977,10 @@
         <v>69</v>
       </c>
       <c r="N16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
@@ -1994,37 +1994,37 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" t="s">
         <v>101</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>102</v>
       </c>
-      <c r="C17" t="s">
+      <c r="E17" t="s">
         <v>103</v>
-      </c>
-      <c r="D17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17" t="s">
-        <v>105</v>
       </c>
       <c r="F17" t="s">
         <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I17" t="s">
         <v>26</v>
       </c>
       <c r="J17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L17" t="s">
         <v>68</v>
@@ -2033,10 +2033,10 @@
         <v>69</v>
       </c>
       <c r="N17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -2050,37 +2050,37 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" t="s">
         <v>101</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
         <v>102</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
         <v>103</v>
-      </c>
-      <c r="D18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" t="s">
-        <v>105</v>
       </c>
       <c r="F18" t="s">
         <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I18" t="s">
         <v>26</v>
       </c>
       <c r="J18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s">
         <v>68</v>
@@ -2089,10 +2089,10 @@
         <v>69</v>
       </c>
       <c r="N18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -2106,37 +2106,37 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
         <v>101</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
         <v>102</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" t="s">
-        <v>105</v>
       </c>
       <c r="F19" t="s">
         <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I19" t="s">
         <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L19" t="s">
         <v>68</v>
@@ -2145,10 +2145,10 @@
         <v>69</v>
       </c>
       <c r="N19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O19" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -2162,37 +2162,37 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" t="s">
         <v>101</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>102</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>103</v>
-      </c>
-      <c r="D20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" t="s">
-        <v>105</v>
       </c>
       <c r="F20" t="s">
         <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I20" t="s">
         <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s">
         <v>68</v>
@@ -2201,10 +2201,10 @@
         <v>69</v>
       </c>
       <c r="N20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -2218,28 +2218,28 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" t="s">
         <v>122</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>123</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>124</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H21" t="s">
         <v>125</v>
-      </c>
-      <c r="G21" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" t="s">
-        <v>127</v>
       </c>
       <c r="I21" t="s">
         <v>26</v>
@@ -2274,28 +2274,28 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" t="s">
         <v>122</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>123</v>
       </c>
-      <c r="E22" t="s">
-        <v>124</v>
-      </c>
-      <c r="F22" t="s">
-        <v>125</v>
-      </c>
       <c r="G22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I22" t="s">
         <v>26</v>
@@ -2330,28 +2330,28 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" t="s">
         <v>122</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>123</v>
       </c>
-      <c r="E23" t="s">
-        <v>124</v>
-      </c>
-      <c r="F23" t="s">
-        <v>125</v>
-      </c>
       <c r="G23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I23" t="s">
         <v>26</v>
@@ -2386,28 +2386,28 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" t="s">
         <v>122</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>123</v>
       </c>
-      <c r="E24" t="s">
-        <v>124</v>
-      </c>
-      <c r="F24" t="s">
-        <v>125</v>
-      </c>
       <c r="G24" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H24" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I24" t="s">
         <v>26</v>
@@ -2442,28 +2442,28 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" t="s">
         <v>134</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>135</v>
       </c>
-      <c r="E25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F25" t="s">
-        <v>137</v>
-      </c>
       <c r="G25" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H25" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I25" t="s">
         <v>26</v>
@@ -2481,10 +2481,10 @@
         <v>45</v>
       </c>
       <c r="N25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
@@ -2498,37 +2498,37 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" t="s">
         <v>138</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
         <v>139</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26" t="s">
         <v>140</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>141</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>142</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>143</v>
-      </c>
-      <c r="G26" t="s">
-        <v>144</v>
-      </c>
-      <c r="H26" t="s">
-        <v>145</v>
       </c>
       <c r="I26" t="s">
         <v>42</v>
       </c>
       <c r="J26" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s">
         <v>29</v>
@@ -2537,10 +2537,10 @@
         <v>30</v>
       </c>
       <c r="N26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2554,37 +2554,37 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" t="s">
         <v>138</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
         <v>139</v>
       </c>
-      <c r="C27" t="s">
+      <c r="E27" t="s">
         <v>140</v>
       </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
         <v>141</v>
       </c>
-      <c r="E27" t="s">
-        <v>142</v>
-      </c>
-      <c r="F27" t="s">
-        <v>143</v>
-      </c>
       <c r="G27" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H27" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I27" t="s">
         <v>42</v>
       </c>
       <c r="J27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s">
         <v>29</v>
@@ -2593,10 +2593,10 @@
         <v>30</v>
       </c>
       <c r="N27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2610,28 +2610,28 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" t="s">
         <v>151</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>152</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>153</v>
       </c>
-      <c r="F28" t="s">
+      <c r="H28" t="s">
         <v>154</v>
-      </c>
-      <c r="G28" t="s">
-        <v>155</v>
-      </c>
-      <c r="H28" t="s">
-        <v>156</v>
       </c>
       <c r="I28" t="s">
         <v>26</v>
@@ -2649,10 +2649,10 @@
         <v>30</v>
       </c>
       <c r="N28" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="O28" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
@@ -2666,22 +2666,22 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" t="s">
         <v>151</v>
       </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
         <v>152</v>
-      </c>
-      <c r="E29" t="s">
-        <v>153</v>
-      </c>
-      <c r="F29" t="s">
-        <v>154</v>
       </c>
       <c r="G29" t="s">
         <v>157</v>
@@ -2705,10 +2705,10 @@
         <v>30</v>
       </c>
       <c r="N29" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="O29" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2722,22 +2722,22 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B30" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" t="s">
         <v>151</v>
       </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
         <v>152</v>
-      </c>
-      <c r="E30" t="s">
-        <v>153</v>
-      </c>
-      <c r="F30" t="s">
-        <v>154</v>
       </c>
       <c r="G30" t="s">
         <v>159</v>
@@ -2761,10 +2761,10 @@
         <v>30</v>
       </c>
       <c r="N30" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="O30" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2778,10 +2778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B31" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s">
         <v>161</v>
@@ -2817,10 +2817,10 @@
         <v>30</v>
       </c>
       <c r="N31" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="O31" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2929,10 +2929,10 @@
         <v>69</v>
       </c>
       <c r="N33" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="O33" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
@@ -2985,10 +2985,10 @@
         <v>69</v>
       </c>
       <c r="N34" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="O34" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
@@ -3029,7 +3029,7 @@
         <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K35" t="s">
         <v>28</v>
@@ -3097,10 +3097,10 @@
         <v>30</v>
       </c>
       <c r="N36" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="O36" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -3153,10 +3153,10 @@
         <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="O37" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -3209,10 +3209,10 @@
         <v>30</v>
       </c>
       <c r="N38" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="O38" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3253,10 +3253,10 @@
         <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s">
         <v>29</v>
@@ -3309,10 +3309,10 @@
         <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s">
         <v>29</v>
@@ -3365,10 +3365,10 @@
         <v>26</v>
       </c>
       <c r="J41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K41" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s">
         <v>29</v>
@@ -3489,10 +3489,10 @@
         <v>30</v>
       </c>
       <c r="N43" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="O43" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
@@ -3645,10 +3645,10 @@
         <v>229</v>
       </c>
       <c r="J46" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K46" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s">
         <v>29</v>
@@ -3701,10 +3701,10 @@
         <v>229</v>
       </c>
       <c r="J47" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K47" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s">
         <v>29</v>
@@ -3757,10 +3757,10 @@
         <v>229</v>
       </c>
       <c r="J48" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s">
         <v>29</v>
@@ -3813,10 +3813,10 @@
         <v>229</v>
       </c>
       <c r="J49" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s">
         <v>29</v>
@@ -3869,10 +3869,10 @@
         <v>229</v>
       </c>
       <c r="J50" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L50" t="s">
         <v>29</v>
@@ -3925,10 +3925,10 @@
         <v>229</v>
       </c>
       <c r="J51" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K51" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s">
         <v>29</v>
@@ -3981,10 +3981,10 @@
         <v>229</v>
       </c>
       <c r="J52" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K52" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s">
         <v>29</v>
@@ -4037,10 +4037,10 @@
         <v>229</v>
       </c>
       <c r="J53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K53" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -224,6 +224,12 @@
     <t xml:space="preserve">rolling-3-mean</t>
   </si>
   <si>
+    <t xml:space="preserve">2024M7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M7</t>
+  </si>
+  <si>
     <t xml:space="preserve">Consumer prices</t>
   </si>
   <si>
@@ -237,12 +243,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M7</t>
   </si>
   <si>
     <t xml:space="preserve">Innovation</t>
@@ -1585,10 +1585,10 @@
         <v>69</v>
       </c>
       <c r="N9" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="O9" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1608,28 +1608,28 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" t="s">
         <v>72</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>73</v>
-      </c>
-      <c r="G10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" t="s">
-        <v>71</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K10" t="s">
         <v>28</v>
@@ -1641,10 +1641,10 @@
         <v>30</v>
       </c>
       <c r="N10" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1809,10 +1809,10 @@
         <v>45</v>
       </c>
       <c r="N13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O13" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1865,10 +1865,10 @@
         <v>45</v>
       </c>
       <c r="N14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O14" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -2481,10 +2481,10 @@
         <v>45</v>
       </c>
       <c r="N25" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O25" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
@@ -2929,10 +2929,10 @@
         <v>69</v>
       </c>
       <c r="N33" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="O33" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
@@ -2985,10 +2985,10 @@
         <v>69</v>
       </c>
       <c r="N34" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="O34" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
@@ -3029,7 +3029,7 @@
         <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K35" t="s">
         <v>28</v>
